--- a/docs/Files/Small-format_model/ODYM_T6_SFConsumption_V1.0.xlsx
+++ b/docs/Files/Small-format_model/ODYM_T6_SFConsumption_V1.0.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB8AC7AC-D0D6-4B53-BFFF-3D9CC512F672}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4713F17-CAEB-4169-816E-DF64F3127DCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="4" r:id="rId1"/>
@@ -342,12 +342,6 @@
     <t>Cf. log and ref sheets</t>
   </si>
   <si>
-    <t>EV LIB</t>
-  </si>
-  <si>
-    <t>other EV LIB products</t>
-  </si>
-  <si>
     <t>LIB</t>
   </si>
   <si>
@@ -364,6 +358,12 @@
   </si>
   <si>
     <t>ODYM_Classifications_SF</t>
+  </si>
+  <si>
+    <t>SF LIB</t>
+  </si>
+  <si>
+    <t>other SF LIB products</t>
   </si>
 </sst>
 </file>
@@ -792,7 +792,7 @@
         <v>9</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>4</v>
@@ -806,7 +806,7 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>4</v>
@@ -876,7 +876,7 @@
         <v>21</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>4</v>
@@ -960,7 +960,7 @@
         <v>35</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>4</v>
@@ -1059,7 +1059,7 @@
         <v>57</v>
       </c>
       <c r="F23" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>4</v>
@@ -1148,18 +1148,18 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C1" s="13" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
@@ -5373,7 +5373,7 @@
         <v>2000</v>
       </c>
       <c r="C303">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="D303">
         <v>0</v>
@@ -5387,7 +5387,7 @@
         <v>2001</v>
       </c>
       <c r="C304">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="D304">
         <v>0</v>
@@ -5401,7 +5401,7 @@
         <v>2002</v>
       </c>
       <c r="C305">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="D305">
         <v>0</v>
@@ -5415,7 +5415,7 @@
         <v>2003</v>
       </c>
       <c r="C306">
-        <v>0</v>
+        <v>704</v>
       </c>
       <c r="D306">
         <v>0</v>
@@ -5429,7 +5429,7 @@
         <v>2004</v>
       </c>
       <c r="C307">
-        <v>0</v>
+        <v>1167</v>
       </c>
       <c r="D307">
         <v>0</v>
@@ -5443,7 +5443,7 @@
         <v>2005</v>
       </c>
       <c r="C308">
-        <v>0</v>
+        <v>1867</v>
       </c>
       <c r="D308">
         <v>0</v>
@@ -5457,7 +5457,7 @@
         <v>2006</v>
       </c>
       <c r="C309">
-        <v>0</v>
+        <v>2803</v>
       </c>
       <c r="D309">
         <v>0</v>
@@ -5471,7 +5471,7 @@
         <v>2007</v>
       </c>
       <c r="C310">
-        <v>0</v>
+        <v>3895</v>
       </c>
       <c r="D310">
         <v>0</v>
@@ -5485,7 +5485,7 @@
         <v>2008</v>
       </c>
       <c r="C311">
-        <v>0</v>
+        <v>5003</v>
       </c>
       <c r="D311">
         <v>0</v>
@@ -5499,7 +5499,7 @@
         <v>2009</v>
       </c>
       <c r="C312">
-        <v>0</v>
+        <v>6135</v>
       </c>
       <c r="D312">
         <v>0</v>
@@ -5513,7 +5513,7 @@
         <v>2010</v>
       </c>
       <c r="C313">
-        <v>0.17299999999999999</v>
+        <v>7235</v>
       </c>
       <c r="D313">
         <v>0</v>
@@ -5527,7 +5527,7 @@
         <v>2011</v>
       </c>
       <c r="C314">
-        <v>2.5470000000000002</v>
+        <v>8208</v>
       </c>
       <c r="D314">
         <v>0</v>
@@ -5541,7 +5541,7 @@
         <v>2012</v>
       </c>
       <c r="C315">
-        <v>6.1829999999999998</v>
+        <v>8957</v>
       </c>
       <c r="D315">
         <v>0</v>
@@ -5555,7 +5555,7 @@
         <v>2013</v>
       </c>
       <c r="C316">
-        <v>13.468999999999999</v>
+        <v>9632</v>
       </c>
       <c r="D316">
         <v>0</v>
@@ -5569,7 +5569,7 @@
         <v>2014</v>
       </c>
       <c r="C317">
-        <v>14.243</v>
+        <v>10261</v>
       </c>
       <c r="D317">
         <v>0</v>
@@ -5586,7 +5586,7 @@
         <v>2015</v>
       </c>
       <c r="C318">
-        <v>19.106000000000002</v>
+        <v>11064</v>
       </c>
       <c r="D318">
         <v>0</v>
@@ -5600,7 +5600,7 @@
         <v>2016</v>
       </c>
       <c r="C319">
-        <v>28.478000000000002</v>
+        <v>12271</v>
       </c>
       <c r="D319">
         <v>0</v>
@@ -5614,7 +5614,7 @@
         <v>2017</v>
       </c>
       <c r="C320">
-        <v>34.33</v>
+        <v>14164</v>
       </c>
       <c r="D320">
         <v>0</v>
@@ -5628,7 +5628,7 @@
         <v>2018</v>
       </c>
       <c r="C321">
-        <v>85.921000000000006</v>
+        <v>16772</v>
       </c>
       <c r="D321">
         <v>0</v>
@@ -5642,7 +5642,7 @@
         <v>2019</v>
       </c>
       <c r="C322">
-        <v>88.271000000000001</v>
+        <v>19829</v>
       </c>
       <c r="D322">
         <v>0</v>
@@ -5656,7 +5656,7 @@
         <v>2020</v>
       </c>
       <c r="C323">
-        <v>106.196</v>
+        <v>23041</v>
       </c>
       <c r="D323">
         <v>0</v>
@@ -5670,7 +5670,7 @@
         <v>2021</v>
       </c>
       <c r="C324">
-        <v>144.52500000000001</v>
+        <v>26327</v>
       </c>
       <c r="D324">
         <v>0</v>
@@ -5684,7 +5684,7 @@
         <v>2022</v>
       </c>
       <c r="C325">
-        <v>282.14299999999997</v>
+        <v>29498</v>
       </c>
       <c r="D325">
         <v>0</v>
@@ -5698,7 +5698,7 @@
         <v>2023</v>
       </c>
       <c r="C326">
-        <v>440.94099999999997</v>
+        <v>32575</v>
       </c>
       <c r="D326">
         <v>0</v>
@@ -5712,7 +5712,7 @@
         <v>2024</v>
       </c>
       <c r="C327">
-        <v>501.92</v>
+        <v>35330</v>
       </c>
       <c r="D327">
         <v>0</v>
